--- a/output/pdf_financials_xlsx/APX.xlsx
+++ b/output/pdf_financials_xlsx/APX.xlsx
@@ -5974,49 +5974,49 @@
         <v>3.298134</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>3.298582</v>
+        <v>3.303165</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>3.676275</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>3.933518</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>3.934741</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>3.934741</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>3.934741</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>3.934741</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>4.049741</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>4.049741</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>4.055079</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>4.370179</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>4.765259</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>4.765259</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>5.236081</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>5.514963</v>
       </c>
     </row>
     <row r="93">
@@ -10297,7 +10297,11 @@
           <t>Warrants reserve 6</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -10396,7 +10400,11 @@
           <t>Share-based payments reserve 6</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -11289,7 +11297,11 @@
           <t>Warrants reserve 7</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -11380,7 +11392,11 @@
           <t>Share-based payments reserve 7</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
@@ -13062,7 +13078,11 @@
           <t>Warrants reserve (Note 8)</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
@@ -13151,7 +13171,11 @@
           <t>Share-based payments reserve (Note 8)</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
@@ -13709,7 +13733,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -14188,7 +14216,11 @@
           <t>Warrants reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
@@ -15085,7 +15117,11 @@
           <t>Warrants reserve (Note 10)</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
@@ -17743,7 +17779,11 @@
           <t>Share-based payments reserve 3,307,659</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/APX.xlsx
+++ b/output/pdf_financials_xlsx/APX.xlsx
@@ -950,31 +950,31 @@
         <v>0.737771</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.509316</v>
+        <v>0.584176</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.459711</v>
+        <v>0.7365429999999999</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.403168</v>
+        <v>0.459262</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.363301</v>
+        <v>0.429849</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.357993</v>
+        <v>0.417423</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.33933</v>
+        <v>0.396698</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.364671</v>
+        <v>0.532416</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.376</v>
+        <v>0.447173</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.352638</v>
+        <v>0.438414</v>
       </c>
       <c r="N10" s="3" t="n">
         <v>0.343647</v>
@@ -1012,7 +1012,7 @@
         <v>-0.737771</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.509316</v>
+        <v>-0.584176</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>-0.7365429999999999</v>
@@ -1080,37 +1080,37 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.000827</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.003625</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.002489</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.001502</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.00119</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.003448</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.001387</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.00022</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>8.000000000000001e-05</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.000546</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.001123</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>0</v>
@@ -2088,37 +2088,37 @@
         <v>-0.766543</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-2.160369</v>
+        <v>-2.161196</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.490141</v>
+        <v>-0.493766</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-3.158604</v>
+        <v>-3.161093</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.08459800000000001</v>
+        <v>0.083096</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.071394</v>
+        <v>-0.072584</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.3851</v>
+        <v>-0.388548</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.469638</v>
+        <v>-0.471025</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.414837</v>
+        <v>-0.415057</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.6152609999999999</v>
+        <v>-0.615341</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.327529</v>
+        <v>-0.328075</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-0.651264</v>
+        <v>-0.6523870000000001</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>-0.340059</v>
@@ -2212,37 +2212,37 @@
         <v>-0.765128</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-2.159916</v>
+        <v>-2.160743</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.490141</v>
+        <v>-0.493766</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-3.158604</v>
+        <v>-3.161093</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.08459800000000001</v>
+        <v>0.083096</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.071394</v>
+        <v>-0.072584</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.3851</v>
+        <v>-0.388548</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.469638</v>
+        <v>-0.471025</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.414837</v>
+        <v>-0.415057</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.6152609999999999</v>
+        <v>-0.615341</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.327529</v>
+        <v>-0.328075</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.651264</v>
+        <v>-0.6523870000000001</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>-0.340059</v>
@@ -2514,49 +2514,49 @@
         <v>0.013629</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.013629</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.187177</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.032689</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.00703</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.000402</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.019026</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.254183</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.137346</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.100231</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.022372</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.189952</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.034631</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.006908</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.007842999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -2630,49 +2630,49 @@
         <v>1.773629</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>1.76</v>
+        <v>1.773629</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.065</v>
+        <v>0.252177</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>0.363</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.0525</v>
+        <v>0.085189</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.531</v>
+        <v>0.53803</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.021333</v>
+        <v>0.021735</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.276334</v>
+        <v>0.29536</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.346167</v>
+        <v>0.6003500000000001</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.297792</v>
+        <v>0.435138</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.044167</v>
+        <v>0.144398</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.1905</v>
+        <v>0.212872</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.077167</v>
+        <v>0.267119</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.037667</v>
+        <v>0.072298</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.030917</v>
+        <v>0.037825</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0.014175</v>
+        <v>0.022018</v>
       </c>
     </row>
     <row r="37">
@@ -3326,49 +3326,49 @@
         <v>0.024464</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.038093</v>
+        <v>0.024464</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.016366</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0.014106</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.040994</v>
+        <v>0.008305</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.016482</v>
+        <v>0.009452</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.150695</v>
+        <v>0.150293</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.023589</v>
+        <v>0.004563</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.258042</v>
+        <v>0.003859</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.139954</v>
+        <v>0.002608</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.102839</v>
+        <v>0.002608</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.040243</v>
+        <v>0.017871</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.191988</v>
+        <v>0.002036</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.036729</v>
+        <v>0.002098</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.010864</v>
+        <v>0.003956</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.087099</v>
+        <v>0.07925599999999999</v>
       </c>
     </row>
     <row r="49">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -9412,7 +9412,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>-</t>
@@ -12528,7 +12532,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E41" s="5" t="n">
         <v>0.02217</v>
       </c>
@@ -15941,7 +15949,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -16868,7 +16876,11 @@
           <t>Reclamation deposits 21,120</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>-</t>
@@ -18276,7 +18288,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -19199,7 +19211,11 @@
           <t>Reclamation Deposits</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
@@ -28440,7 +28456,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E201" t="inlineStr">
         <is>
           <t>-</t>
@@ -37361,7 +37381,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -43560,7 +43580,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -43750,7 +43770,7 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
@@ -44831,7 +44851,7 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
